--- a/data/3FEB_25_26/players_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/players_25_26_3FEB.xlsx
@@ -13391,10 +13391,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>263.6833333333333</v>
+        <v>278.5</v>
       </c>
       <c r="B140" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C140" t="n">
         <v>5</v>
@@ -13403,10 +13403,10 @@
         <v>11</v>
       </c>
       <c r="E140" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F140" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G140" t="n">
         <v>9</v>
@@ -13418,10 +13418,10 @@
         <v>6</v>
       </c>
       <c r="J140" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K140" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L140" t="n">
         <v>2</v>
@@ -13430,10 +13430,10 @@
         <v>12</v>
       </c>
       <c r="N140" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O140" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P140" t="n">
         <v>1</v>
@@ -13469,7 +13469,7 @@
         </is>
       </c>
       <c r="W140" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
@@ -13484,10 +13484,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>199.2666666666667</v>
+        <v>214.3833333333333</v>
       </c>
       <c r="B141" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C141" t="n">
         <v>7</v>
@@ -13496,25 +13496,25 @@
         <v>11</v>
       </c>
       <c r="E141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F141" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G141" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H141" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I141" t="n">
         <v>10</v>
       </c>
       <c r="J141" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L141" t="n">
         <v>7</v>
@@ -13523,10 +13523,10 @@
         <v>8</v>
       </c>
       <c r="N141" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O141" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="W141" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
@@ -13577,16 +13577,16 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>328.1833333333333</v>
+        <v>335.5</v>
       </c>
       <c r="B142" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C142" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D142" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E142" t="n">
         <v>1</v>
@@ -13598,31 +13598,31 @@
         <v>16</v>
       </c>
       <c r="H142" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I142" t="n">
         <v>37</v>
       </c>
       <c r="J142" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K142" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L142" t="n">
         <v>14</v>
       </c>
       <c r="M142" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N142" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="O142" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P142" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         </is>
       </c>
       <c r="W142" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
@@ -13670,49 +13670,49 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>689.25</v>
+        <v>714.1833333333333</v>
       </c>
       <c r="B143" t="n">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C143" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D143" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E143" t="n">
         <v>26</v>
       </c>
       <c r="F143" t="n">
+        <v>91</v>
+      </c>
+      <c r="G143" t="n">
+        <v>90</v>
+      </c>
+      <c r="H143" t="n">
+        <v>118</v>
+      </c>
+      <c r="I143" t="n">
+        <v>51</v>
+      </c>
+      <c r="J143" t="n">
         <v>89</v>
       </c>
-      <c r="G143" t="n">
-        <v>85</v>
-      </c>
-      <c r="H143" t="n">
-        <v>111</v>
-      </c>
-      <c r="I143" t="n">
-        <v>47</v>
-      </c>
-      <c r="J143" t="n">
-        <v>86</v>
-      </c>
       <c r="K143" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L143" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M143" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N143" t="n">
         <v>54</v>
       </c>
       <c r="O143" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P143" t="n">
         <v>24</v>
@@ -13748,7 +13748,7 @@
         </is>
       </c>
       <c r="W143" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
@@ -13763,49 +13763,49 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>331.0166666666667</v>
+        <v>343.6333333333333</v>
       </c>
       <c r="B144" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C144" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D144" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E144" t="n">
         <v>10</v>
       </c>
       <c r="F144" t="n">
+        <v>27</v>
+      </c>
+      <c r="G144" t="n">
+        <v>21</v>
+      </c>
+      <c r="H144" t="n">
+        <v>33</v>
+      </c>
+      <c r="I144" t="n">
         <v>26</v>
-      </c>
-      <c r="G144" t="n">
-        <v>17</v>
-      </c>
-      <c r="H144" t="n">
-        <v>28</v>
-      </c>
-      <c r="I144" t="n">
-        <v>25</v>
       </c>
       <c r="J144" t="n">
         <v>22</v>
       </c>
       <c r="K144" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L144" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M144" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N144" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O144" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P144" t="n">
         <v>4</v>
@@ -13841,7 +13841,7 @@
         </is>
       </c>
       <c r="W144" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
@@ -13856,49 +13856,49 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>639.6333333333333</v>
+        <v>664.4333333333333</v>
       </c>
       <c r="B145" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C145" t="n">
         <v>33</v>
       </c>
       <c r="D145" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E145" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F145" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G145" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H145" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I145" t="n">
         <v>55</v>
       </c>
       <c r="J145" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="K145" t="n">
         <v>19</v>
       </c>
       <c r="L145" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M145" t="n">
         <v>27</v>
       </c>
       <c r="N145" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O145" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P145" t="n">
         <v>9</v>
@@ -13934,7 +13934,7 @@
         </is>
       </c>
       <c r="W145" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X145" t="inlineStr">
         <is>
@@ -13949,52 +13949,52 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>419.4833333333333</v>
+        <v>451.4666666666667</v>
       </c>
       <c r="B146" t="n">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="C146" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D146" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G146" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H146" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I146" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J146" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="K146" t="n">
         <v>10</v>
       </c>
       <c r="L146" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M146" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N146" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O146" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="P146" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         </is>
       </c>
       <c r="W146" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
@@ -14135,22 +14135,22 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>324.4</v>
+        <v>347.25</v>
       </c>
       <c r="B148" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C148" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D148" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E148" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F148" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G148" t="n">
         <v>14</v>
@@ -14162,22 +14162,22 @@
         <v>10</v>
       </c>
       <c r="J148" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K148" t="n">
         <v>16</v>
       </c>
       <c r="L148" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M148" t="n">
         <v>19</v>
       </c>
       <c r="N148" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O148" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P148" t="n">
         <v>2</v>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="W148" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>112.55</v>
+        <v>125.7833333333333</v>
       </c>
       <c r="B149" t="n">
         <v>22</v>
@@ -14243,7 +14243,7 @@
         <v>7</v>
       </c>
       <c r="F149" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G149" t="n">
         <v>1</v>
@@ -14255,7 +14255,7 @@
         <v>3</v>
       </c>
       <c r="J149" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K149" t="n">
         <v>4</v>
@@ -14264,10 +14264,10 @@
         <v>3</v>
       </c>
       <c r="M149" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N149" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O149" t="n">
         <v>5</v>
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="W149" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
@@ -14321,49 +14321,49 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>724.7333333333333</v>
+        <v>757.0666666666667</v>
       </c>
       <c r="B150" t="n">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="C150" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D150" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E150" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F150" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="G150" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H150" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="I150" t="n">
         <v>15</v>
       </c>
       <c r="J150" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K150" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="L150" t="n">
         <v>55</v>
       </c>
       <c r="M150" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N150" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O150" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="P150" t="n">
         <v>3</v>
@@ -14399,7 +14399,7 @@
         </is>
       </c>
       <c r="W150" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
@@ -15902,49 +15902,49 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>680.3666666666667</v>
+        <v>709.3833333333333</v>
       </c>
       <c r="B167" t="n">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="C167" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D167" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E167" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F167" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="G167" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H167" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I167" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J167" t="n">
         <v>68</v>
       </c>
       <c r="K167" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L167" t="n">
         <v>21</v>
       </c>
       <c r="M167" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N167" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="O167" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P167" t="n">
         <v>1</v>
@@ -15980,7 +15980,7 @@
         </is>
       </c>
       <c r="W167" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
@@ -15995,22 +15995,22 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>577.8333333333334</v>
+        <v>603.55</v>
       </c>
       <c r="B168" t="n">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C168" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D168" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E168" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F168" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G168" t="n">
         <v>51</v>
@@ -16019,25 +16019,25 @@
         <v>71</v>
       </c>
       <c r="I168" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J168" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K168" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L168" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M168" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N168" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="O168" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P168" t="n">
         <v>7</v>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="W168" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
@@ -16088,49 +16088,49 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>567.8666666666667</v>
+        <v>602.5166666666667</v>
       </c>
       <c r="B169" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C169" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D169" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E169" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F169" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G169" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H169" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I169" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J169" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="K169" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L169" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M169" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N169" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O169" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P169" t="n">
         <v>2</v>
@@ -16166,7 +16166,7 @@
         </is>
       </c>
       <c r="W169" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>21.56666666666667</v>
+        <v>24.15</v>
       </c>
       <c r="B171" t="n">
         <v>6</v>
@@ -16301,7 +16301,7 @@
         <v>1</v>
       </c>
       <c r="J171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K171" t="n">
         <v>1</v>
@@ -16352,7 +16352,7 @@
         </is>
       </c>
       <c r="W171" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X171" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>520.6166666666667</v>
+        <v>540.2833333333333</v>
       </c>
       <c r="B172" t="n">
         <v>139</v>
@@ -16382,7 +16382,7 @@
         <v>15</v>
       </c>
       <c r="F172" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G172" t="n">
         <v>28</v>
@@ -16394,10 +16394,10 @@
         <v>18</v>
       </c>
       <c r="J172" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K172" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L172" t="n">
         <v>21</v>
@@ -16406,7 +16406,7 @@
         <v>35</v>
       </c>
       <c r="N172" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O172" t="n">
         <v>45</v>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="W172" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X172" t="inlineStr">
         <is>
@@ -16646,17 +16646,17 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>161.1</v>
+        <v>178.8666666666667</v>
       </c>
       <c r="B175" t="n">
+        <v>49</v>
+      </c>
+      <c r="C175" t="n">
+        <v>20</v>
+      </c>
+      <c r="D175" t="n">
         <v>39</v>
       </c>
-      <c r="C175" t="n">
-        <v>16</v>
-      </c>
-      <c r="D175" t="n">
-        <v>33</v>
-      </c>
       <c r="E175" t="n">
         <v>0</v>
       </c>
@@ -16664,31 +16664,31 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
+        <v>9</v>
+      </c>
+      <c r="H175" t="n">
+        <v>14</v>
+      </c>
+      <c r="I175" t="n">
+        <v>22</v>
+      </c>
+      <c r="J175" t="n">
+        <v>23</v>
+      </c>
+      <c r="K175" t="n">
         <v>7</v>
-      </c>
-      <c r="H175" t="n">
-        <v>12</v>
-      </c>
-      <c r="I175" t="n">
-        <v>20</v>
-      </c>
-      <c r="J175" t="n">
-        <v>21</v>
-      </c>
-      <c r="K175" t="n">
-        <v>6</v>
       </c>
       <c r="L175" t="n">
         <v>4</v>
       </c>
       <c r="M175" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N175" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O175" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P175" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="W175" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X175" t="inlineStr">
         <is>
@@ -16739,49 +16739,49 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>546.6666666666666</v>
+        <v>563.4333333333333</v>
       </c>
       <c r="B176" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C176" t="n">
         <v>31</v>
       </c>
       <c r="D176" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E176" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F176" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G176" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H176" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I176" t="n">
         <v>10</v>
       </c>
       <c r="J176" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K176" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L176" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M176" t="n">
         <v>46</v>
       </c>
       <c r="N176" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O176" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="P176" t="n">
         <v>0</v>
@@ -16817,7 +16817,7 @@
         </is>
       </c>
       <c r="W176" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X176" t="inlineStr">
         <is>
@@ -16832,52 +16832,52 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>429.4666666666666</v>
+        <v>451.5666666666667</v>
       </c>
       <c r="B177" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C177" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D177" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E177" t="n">
         <v>4</v>
       </c>
       <c r="F177" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G177" t="n">
+        <v>18</v>
+      </c>
+      <c r="H177" t="n">
+        <v>40</v>
+      </c>
+      <c r="I177" t="n">
+        <v>39</v>
+      </c>
+      <c r="J177" t="n">
+        <v>74</v>
+      </c>
+      <c r="K177" t="n">
         <v>16</v>
-      </c>
-      <c r="H177" t="n">
-        <v>38</v>
-      </c>
-      <c r="I177" t="n">
-        <v>37</v>
-      </c>
-      <c r="J177" t="n">
-        <v>71</v>
-      </c>
-      <c r="K177" t="n">
-        <v>14</v>
       </c>
       <c r="L177" t="n">
         <v>13</v>
       </c>
       <c r="M177" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N177" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O177" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P177" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         </is>
       </c>
       <c r="W177" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X177" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>300.0833333333333</v>
+        <v>304.6166666666667</v>
       </c>
       <c r="B178" t="n">
         <v>134</v>
@@ -16934,7 +16934,7 @@
         <v>37</v>
       </c>
       <c r="D178" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -16949,25 +16949,25 @@
         <v>85</v>
       </c>
       <c r="I178" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J178" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K178" t="n">
         <v>12</v>
       </c>
       <c r="L178" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M178" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N178" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O178" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P178" t="n">
         <v>2</v>
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="W178" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
@@ -17018,16 +17018,16 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>559.0166666666667</v>
+        <v>586.2166666666667</v>
       </c>
       <c r="B179" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="C179" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D179" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E179" t="n">
         <v>3</v>
@@ -17036,31 +17036,31 @@
         <v>10</v>
       </c>
       <c r="G179" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H179" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I179" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J179" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K179" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L179" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M179" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N179" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O179" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="P179" t="n">
         <v>7</v>
@@ -17096,7 +17096,7 @@
         </is>
       </c>
       <c r="W179" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X179" t="inlineStr">
         <is>
@@ -18878,10 +18878,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>511.3166666666667</v>
+        <v>527.6166666666667</v>
       </c>
       <c r="B199" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C199" t="n">
         <v>29</v>
@@ -18890,37 +18890,37 @@
         <v>53</v>
       </c>
       <c r="E199" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F199" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G199" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H199" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I199" t="n">
         <v>18</v>
       </c>
       <c r="J199" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K199" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L199" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M199" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N199" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O199" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P199" t="n">
         <v>0</v>
@@ -18956,7 +18956,7 @@
         </is>
       </c>
       <c r="W199" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X199" t="inlineStr">
         <is>
@@ -18971,22 +18971,22 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>571.0166666666667</v>
+        <v>584.3333333333334</v>
       </c>
       <c r="B200" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C200" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D200" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E200" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F200" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G200" t="n">
         <v>20</v>
@@ -18995,10 +18995,10 @@
         <v>28</v>
       </c>
       <c r="I200" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J200" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K200" t="n">
         <v>16</v>
@@ -19007,16 +19007,16 @@
         <v>18</v>
       </c>
       <c r="M200" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N200" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O200" t="n">
         <v>39</v>
       </c>
       <c r="P200" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         </is>
       </c>
       <c r="W200" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X200" t="inlineStr">
         <is>
@@ -19064,40 +19064,40 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>480.2166666666667</v>
+        <v>509.9666666666667</v>
       </c>
       <c r="B201" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="C201" t="n">
         <v>24</v>
       </c>
       <c r="D201" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E201" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F201" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G201" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H201" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I201" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J201" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K201" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L201" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M201" t="n">
         <v>24</v>
@@ -19106,7 +19106,7 @@
         <v>87</v>
       </c>
       <c r="O201" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="P201" t="n">
         <v>1</v>
@@ -19142,7 +19142,7 @@
         </is>
       </c>
       <c r="W201" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X201" t="inlineStr">
         <is>
@@ -19157,22 +19157,22 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>97.53333333333333</v>
+        <v>104.0166666666667</v>
       </c>
       <c r="B202" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C202" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D202" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E202" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F202" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G202" t="n">
         <v>10</v>
@@ -19184,7 +19184,7 @@
         <v>5</v>
       </c>
       <c r="J202" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K202" t="n">
         <v>13</v>
@@ -19193,10 +19193,10 @@
         <v>1</v>
       </c>
       <c r="M202" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N202" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O202" t="n">
         <v>7</v>
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="W202" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X202" t="inlineStr">
         <is>
@@ -19250,49 +19250,49 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>556.2333333333333</v>
+        <v>583.3333333333334</v>
       </c>
       <c r="B203" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C203" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D203" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E203" t="n">
+        <v>18</v>
+      </c>
+      <c r="F203" t="n">
+        <v>52</v>
+      </c>
+      <c r="G203" t="n">
+        <v>34</v>
+      </c>
+      <c r="H203" t="n">
+        <v>60</v>
+      </c>
+      <c r="I203" t="n">
         <v>16</v>
       </c>
-      <c r="F203" t="n">
-        <v>49</v>
-      </c>
-      <c r="G203" t="n">
-        <v>32</v>
-      </c>
-      <c r="H203" t="n">
+      <c r="J203" t="n">
         <v>56</v>
       </c>
-      <c r="I203" t="n">
-        <v>14</v>
-      </c>
-      <c r="J203" t="n">
-        <v>51</v>
-      </c>
       <c r="K203" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L203" t="n">
         <v>19</v>
       </c>
       <c r="M203" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N203" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O203" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P203" t="n">
         <v>7</v>
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="W203" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
@@ -19529,49 +19529,49 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>596.9833333333333</v>
+        <v>614.9499999999999</v>
       </c>
       <c r="B206" t="n">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="C206" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D206" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E206" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F206" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G206" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="H206" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I206" t="n">
         <v>9</v>
       </c>
       <c r="J206" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K206" t="n">
         <v>60</v>
       </c>
       <c r="L206" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M206" t="n">
         <v>35</v>
       </c>
       <c r="N206" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O206" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="P206" t="n">
         <v>6</v>
@@ -19607,7 +19607,7 @@
         </is>
       </c>
       <c r="W206" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
@@ -19622,85 +19622,85 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>407.4333333333333</v>
+        <v>431.5333333333333</v>
       </c>
       <c r="B207" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C207" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D207" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E207" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F207" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G207" t="n">
         <v>40</v>
       </c>
       <c r="H207" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I207" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J207" t="n">
         <v>55</v>
       </c>
       <c r="K207" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L207" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M207" t="n">
+        <v>25</v>
+      </c>
+      <c r="N207" t="n">
+        <v>66</v>
+      </c>
+      <c r="O207" t="n">
+        <v>41</v>
+      </c>
+      <c r="P207" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>https://imagenes.feb.es/Foto.aspx?c=2189198</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>FERNANDEZ SHEPHARD, BREZO</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=982360&amp;c=2189198</t>
+        </is>
+      </c>
+      <c r="W207" t="n">
         <v>24</v>
-      </c>
-      <c r="N207" t="n">
-        <v>62</v>
-      </c>
-      <c r="O207" t="n">
-        <v>37</v>
-      </c>
-      <c r="P207" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R207" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>https://imagenes.feb.es/Foto.aspx?c=2189198</t>
-        </is>
-      </c>
-      <c r="T207" t="inlineStr">
-        <is>
-          <t>FERNANDEZ SHEPHARD, BREZO</t>
-        </is>
-      </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=982360&amp;c=2189198</t>
-        </is>
-      </c>
-      <c r="W207" t="n">
-        <v>23</v>
       </c>
       <c r="X207" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>83.43333333333334</v>
+        <v>90.71666666666667</v>
       </c>
       <c r="B209" t="n">
         <v>8</v>
@@ -19847,7 +19847,7 @@
         <v>10</v>
       </c>
       <c r="N209" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O209" t="n">
         <v>2</v>
@@ -19886,7 +19886,7 @@
         </is>
       </c>
       <c r="W209" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
@@ -20087,16 +20087,16 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>308.3666666666667</v>
+        <v>326.5</v>
       </c>
       <c r="B212" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C212" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D212" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E212" t="n">
         <v>0</v>
@@ -20105,67 +20105,67 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H212" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I212" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J212" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K212" t="n">
         <v>3</v>
       </c>
       <c r="L212" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M212" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N212" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O212" t="n">
+        <v>26</v>
+      </c>
+      <c r="P212" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>https://imagenes.feb.es/Foto.aspx?c=2818405</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>KHIVRENKO, MAKAR</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=982360&amp;c=2818405</t>
+        </is>
+      </c>
+      <c r="W212" t="n">
         <v>24</v>
-      </c>
-      <c r="P212" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R212" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>https://imagenes.feb.es/Foto.aspx?c=2818405</t>
-        </is>
-      </c>
-      <c r="T212" t="inlineStr">
-        <is>
-          <t>KHIVRENKO, MAKAR</t>
-        </is>
-      </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=982360&amp;c=2818405</t>
-        </is>
-      </c>
-      <c r="W212" t="n">
-        <v>23</v>
       </c>
       <c r="X212" t="inlineStr">
         <is>
@@ -20180,22 +20180,22 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>475.7333333333333</v>
+        <v>497.2</v>
       </c>
       <c r="B213" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C213" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D213" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E213" t="n">
         <v>22</v>
       </c>
       <c r="F213" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G213" t="n">
         <v>45</v>
@@ -20207,19 +20207,19 @@
         <v>10</v>
       </c>
       <c r="J213" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K213" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L213" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M213" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="N213" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O213" t="n">
         <v>57</v>
@@ -20258,7 +20258,7 @@
         </is>
       </c>
       <c r="W213" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X213" t="inlineStr">
         <is>
@@ -20273,16 +20273,16 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>395.3333333333334</v>
+        <v>413.4333333333333</v>
       </c>
       <c r="B214" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C214" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D214" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E214" t="n">
         <v>0</v>
@@ -20291,34 +20291,34 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H214" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I214" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J214" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K214" t="n">
         <v>4</v>
       </c>
       <c r="L214" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M214" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N214" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O214" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P214" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         </is>
       </c>
       <c r="W214" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X214" t="inlineStr">
         <is>
@@ -20366,49 +20366,49 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>616.4666666666667</v>
+        <v>642.7333333333333</v>
       </c>
       <c r="B215" t="n">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="C215" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D215" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="E215" t="n">
         <v>33</v>
       </c>
       <c r="F215" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G215" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H215" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="I215" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J215" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K215" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L215" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M215" t="n">
         <v>55</v>
       </c>
       <c r="N215" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O215" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="P215" t="n">
         <v>6</v>
@@ -20444,7 +20444,7 @@
         </is>
       </c>
       <c r="W215" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X215" t="inlineStr">
         <is>
@@ -20459,16 +20459,16 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>353.2333333333333</v>
+        <v>367.9166666666666</v>
       </c>
       <c r="B216" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C216" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D216" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E216" t="n">
         <v>3</v>
@@ -20480,13 +20480,13 @@
         <v>14</v>
       </c>
       <c r="H216" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I216" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J216" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K216" t="n">
         <v>13</v>
@@ -20495,16 +20495,16 @@
         <v>8</v>
       </c>
       <c r="M216" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N216" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O216" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P216" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="W216" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X216" t="inlineStr">
         <is>
@@ -20552,34 +20552,34 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>538.7</v>
+        <v>558.9833333333333</v>
       </c>
       <c r="B217" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C217" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D217" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E217" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F217" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G217" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H217" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I217" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J217" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K217" t="n">
         <v>30</v>
@@ -20588,13 +20588,13 @@
         <v>22</v>
       </c>
       <c r="M217" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N217" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O217" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P217" t="n">
         <v>2</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="W217" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X217" t="inlineStr">
         <is>
@@ -20831,16 +20831,16 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>219.9</v>
+        <v>245.2166666666667</v>
       </c>
       <c r="B220" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C220" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D220" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E220" t="n">
         <v>0</v>
@@ -20849,16 +20849,16 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H220" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I220" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J220" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K220" t="n">
         <v>1</v>
@@ -20870,10 +20870,10 @@
         <v>9</v>
       </c>
       <c r="N220" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O220" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P220" t="n">
         <v>5</v>
@@ -20909,7 +20909,7 @@
         </is>
       </c>
       <c r="W220" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X220" t="inlineStr">
         <is>
@@ -20924,22 +20924,22 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>379.5333333333333</v>
+        <v>403.8833333333333</v>
       </c>
       <c r="B221" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C221" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D221" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E221" t="n">
         <v>17</v>
       </c>
       <c r="F221" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G221" t="n">
         <v>23</v>
@@ -20951,19 +20951,19 @@
         <v>2</v>
       </c>
       <c r="J221" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K221" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="L221" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M221" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N221" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O221" t="n">
         <v>37</v>
@@ -21002,7 +21002,7 @@
         </is>
       </c>
       <c r="W221" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X221" t="inlineStr">
         <is>
@@ -21017,16 +21017,16 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>215.2</v>
+        <v>218.9333333333333</v>
       </c>
       <c r="B222" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C222" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D222" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E222" t="n">
         <v>1</v>
@@ -21038,13 +21038,13 @@
         <v>4</v>
       </c>
       <c r="H222" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I222" t="n">
         <v>5</v>
       </c>
       <c r="J222" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K222" t="n">
         <v>12</v>
@@ -21056,10 +21056,10 @@
         <v>17</v>
       </c>
       <c r="N222" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O222" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P222" t="n">
         <v>1</v>
@@ -21095,7 +21095,7 @@
         </is>
       </c>
       <c r="W222" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X222" t="inlineStr">
         <is>
@@ -21110,16 +21110,16 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>436.8666666666667</v>
+        <v>462</v>
       </c>
       <c r="B223" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C223" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D223" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E223" t="n">
         <v>7</v>
@@ -21128,31 +21128,31 @@
         <v>25</v>
       </c>
       <c r="G223" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H223" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I223" t="n">
         <v>9</v>
       </c>
       <c r="J223" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K223" t="n">
         <v>19</v>
       </c>
       <c r="L223" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M223" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N223" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="O223" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="P223" t="n">
         <v>11</v>
@@ -21188,7 +21188,7 @@
         </is>
       </c>
       <c r="W223" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X223" t="inlineStr">
         <is>
@@ -21203,85 +21203,85 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>506.2833333333334</v>
+        <v>521.9333333333333</v>
       </c>
       <c r="B224" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C224" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D224" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E224" t="n">
         <v>17</v>
       </c>
       <c r="F224" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G224" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H224" t="n">
+        <v>25</v>
+      </c>
+      <c r="I224" t="n">
+        <v>5</v>
+      </c>
+      <c r="J224" t="n">
+        <v>38</v>
+      </c>
+      <c r="K224" t="n">
+        <v>55</v>
+      </c>
+      <c r="L224" t="n">
+        <v>26</v>
+      </c>
+      <c r="M224" t="n">
+        <v>38</v>
+      </c>
+      <c r="N224" t="n">
+        <v>51</v>
+      </c>
+      <c r="O224" t="n">
+        <v>34</v>
+      </c>
+      <c r="P224" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>https://imagenes.feb.es/Foto.aspx?c=2047293</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>SÁNCHEZ GUTIERREZ, PABLO ARIDANY</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=982361&amp;c=2047293</t>
+        </is>
+      </c>
+      <c r="W224" t="n">
         <v>23</v>
-      </c>
-      <c r="I224" t="n">
-        <v>4</v>
-      </c>
-      <c r="J224" t="n">
-        <v>33</v>
-      </c>
-      <c r="K224" t="n">
-        <v>52</v>
-      </c>
-      <c r="L224" t="n">
-        <v>25</v>
-      </c>
-      <c r="M224" t="n">
-        <v>36</v>
-      </c>
-      <c r="N224" t="n">
-        <v>50</v>
-      </c>
-      <c r="O224" t="n">
-        <v>32</v>
-      </c>
-      <c r="P224" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R224" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>https://imagenes.feb.es/Foto.aspx?c=2047293</t>
-        </is>
-      </c>
-      <c r="T224" t="inlineStr">
-        <is>
-          <t>SÁNCHEZ GUTIERREZ, PABLO ARIDANY</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>https://baloncestoenvivo.feb.es/Jugador.aspx?i=982361&amp;c=2047293</t>
-        </is>
-      </c>
-      <c r="W224" t="n">
-        <v>22</v>
       </c>
       <c r="X224" t="inlineStr">
         <is>
@@ -21296,52 +21296,52 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>223.5166666666667</v>
+        <v>246.1666666666667</v>
       </c>
       <c r="B225" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C225" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D225" t="n">
+        <v>43</v>
+      </c>
+      <c r="E225" t="n">
+        <v>14</v>
+      </c>
+      <c r="F225" t="n">
+        <v>47</v>
+      </c>
+      <c r="G225" t="n">
+        <v>6</v>
+      </c>
+      <c r="H225" t="n">
+        <v>9</v>
+      </c>
+      <c r="I225" t="n">
+        <v>22</v>
+      </c>
+      <c r="J225" t="n">
         <v>41</v>
       </c>
-      <c r="E225" t="n">
-        <v>13</v>
-      </c>
-      <c r="F225" t="n">
-        <v>42</v>
-      </c>
-      <c r="G225" t="n">
-        <v>4</v>
-      </c>
-      <c r="H225" t="n">
-        <v>5</v>
-      </c>
-      <c r="I225" t="n">
-        <v>20</v>
-      </c>
-      <c r="J225" t="n">
-        <v>39</v>
-      </c>
       <c r="K225" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L225" t="n">
         <v>7</v>
       </c>
       <c r="M225" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N225" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O225" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="W225" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X225" t="inlineStr">
         <is>
@@ -21482,49 +21482,49 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>411.3666666666667</v>
+        <v>433.3</v>
       </c>
       <c r="B227" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C227" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D227" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E227" t="n">
         <v>24</v>
       </c>
       <c r="F227" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G227" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H227" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I227" t="n">
         <v>3</v>
       </c>
       <c r="J227" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K227" t="n">
         <v>21</v>
       </c>
       <c r="L227" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M227" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N227" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O227" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P227" t="n">
         <v>0</v>
@@ -21560,7 +21560,7 @@
         </is>
       </c>
       <c r="W227" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X227" t="inlineStr">
         <is>
